--- a/STATISTIC-ASSESSMENT.xlsx
+++ b/STATISTIC-ASSESSMENT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4eec18b25c347ea2/Desktop/TOPS_TECHNOLOGY/ASSESSMENT/STAT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AEA4385-597E-455F-BCB8-C32CF8EB260A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{3AEA4385-597E-455F-BCB8-C32CF8EB260A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C77F0EBF-4F7D-454A-A8CD-FFCAE6219E35}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{53A5B192-6451-4C11-83B7-9D80EA01F242}"/>
   </bookViews>
@@ -34,6 +34,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={4C250C57-49B1-4A48-A3E6-9370AD435CCE}</author>
+  </authors>
+  <commentList>
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{4C250C57-49B1-4A48-A3E6-9370AD435CCE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    VARIANCE FOR 2007-08-09 FIGURES AMOUNT COLUM.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={E7EBC230-5729-4A85-AC4D-71A636173F3C}</author>
+  </authors>
+  <commentList>
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{E7EBC230-5729-4A85-AC4D-71A636173F3C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    VARIANCE FOR 1 TO 3 GROUPS COLUM NAME "HEIGHT"</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
   <si>
@@ -158,7 +194,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,8 +232,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -216,6 +264,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="26">
     <border>
@@ -574,7 +628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -667,6 +721,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -690,7 +745,9 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Shruti Gajjar" id="{3291A083-D376-4B16-B4A1-29C295AE7A67}" userId="4eec18b25c347ea2" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -988,12 +1045,28 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="K2" dT="2024-08-01T08:25:37.71" personId="{3291A083-D376-4B16-B4A1-29C295AE7A67}" id="{4C250C57-49B1-4A48-A3E6-9370AD435CCE}">
+    <text>VARIANCE FOR 2007-08-09 FIGURES AMOUNT COLUM.</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="K2" dT="2024-08-01T08:27:21.44" personId="{3291A083-D376-4B16-B4A1-29C295AE7A67}" id="{E7EBC230-5729-4A85-AC4D-71A636173F3C}">
+    <text>VARIANCE FOR 1 TO 3 GROUPS COLUM NAME "HEIGHT"</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0ED9A1A-16C8-42F7-A91E-33DC3E0CF9BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0ED9A1A-16C8-42F7-A91E-33DC3E0CF9BE}">
   <sheetPr codeName="Sheet1">
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:I15"/>
+  <dimension ref="B1:K15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.77734375" customWidth="1"/>
@@ -1002,8 +1075,8 @@
     <col min="9" max="9" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="26" t="s">
         <v>4</v>
       </c>
@@ -1020,8 +1093,9 @@
       <c r="I2" s="7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K2" s="32"/>
+    </row>
+    <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="19" t="s">
         <v>0</v>
       </c>
@@ -1046,7 +1120,7 @@
         <v>6170524.6913580243</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="9">
         <v>39083</v>
       </c>
@@ -1067,7 +1141,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="12">
         <v>39114</v>
       </c>
@@ -1088,7 +1162,7 @@
       </c>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="12">
         <v>39142</v>
       </c>
@@ -1109,7 +1183,7 @@
       </c>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="12">
         <v>39173</v>
       </c>
@@ -1130,7 +1204,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="12">
         <v>39203</v>
       </c>
@@ -1151,7 +1225,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="12">
         <v>39234</v>
       </c>
@@ -1172,7 +1246,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="12">
         <v>39264</v>
       </c>
@@ -1193,7 +1267,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="12">
         <v>39295</v>
       </c>
@@ -1214,7 +1288,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="12">
         <v>39326</v>
       </c>
@@ -1235,7 +1309,7 @@
       </c>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="12">
         <v>39356</v>
       </c>
@@ -1256,7 +1330,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="12">
         <v>39387</v>
       </c>
@@ -1277,7 +1351,7 @@
       </c>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="15">
         <v>39417</v>
       </c>
@@ -1306,23 +1380,24 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2548796E-A169-4F67-9794-9B0BAFF93702}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2548796E-A169-4F67-9794-9B0BAFF93702}">
   <sheetPr codeName="Sheet2">
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:I11"/>
+  <dimension ref="B1:K11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="4" customWidth="1"/>
     <col min="9" max="9" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="28" t="s">
         <v>36</v>
       </c>
@@ -1338,8 +1413,9 @@
       <c r="I2" s="8" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K2" s="32"/>
+    </row>
+    <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>33</v>
       </c>
@@ -1363,7 +1439,7 @@
         <v>9.2619047619047628</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>7</v>
       </c>
@@ -1383,7 +1459,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="12" t="s">
         <v>8</v>
       </c>
@@ -1403,7 +1479,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
         <v>9</v>
       </c>
@@ -1423,7 +1499,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="12" t="s">
         <v>10</v>
       </c>
@@ -1443,7 +1519,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="12" t="s">
         <v>11</v>
       </c>
@@ -1463,7 +1539,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="12" t="s">
         <v>12</v>
       </c>
@@ -1483,7 +1559,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="12" t="s">
         <v>13</v>
       </c>
@@ -1503,7 +1579,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="15" t="s">
         <v>14</v>
       </c>
@@ -1531,5 +1607,6 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>